--- a/dev_stuffs/palmon.xlsx
+++ b/dev_stuffs/palmon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\Palmon\dev_stuffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD62A0F6-0696-45F1-817C-3941B006838F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF999414-7514-47EB-9BB7-63A45EE0B884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{41DCFB66-B5C9-4783-B084-0F93150E63F9}"/>
+    <workbookView xWindow="15735" yWindow="4605" windowWidth="23940" windowHeight="15435" activeTab="2" xr2:uid="{41DCFB66-B5C9-4783-B084-0F93150E63F9}"/>
   </bookViews>
   <sheets>
     <sheet name="材料" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="490">
   <si>
     <t>阶段1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1107,13 +1107,687 @@
   <si>
     <t>强化萤石*</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>etstlib:magic_strike</t>
+  </si>
+  <si>
+    <t>魔法打击：全力打击时将工具的伤害转换为魔法伤害</t>
+  </si>
+  <si>
+    <t>etstlib:critical</t>
+  </si>
+  <si>
+    <t>暴击：全力打击时必定暴击</t>
+  </si>
+  <si>
+    <t>etstlib:armor_piercing</t>
+  </si>
+  <si>
+    <t>护甲穿透：每级提供25%穿甲</t>
+  </si>
+  <si>
+    <t>etstlib:photosynthesis_guide</t>
+  </si>
+  <si>
+    <t>光合制导：你射出的箭矢会略微追踪</t>
+  </si>
+  <si>
+    <t>etstlib:energy_loaded</t>
+  </si>
+  <si>
+    <t>能量装载：你的工具会优先消耗能量存储而非耐久</t>
+  </si>
+  <si>
+    <t>etstlib:short_circuit</t>
+  </si>
+  <si>
+    <t>短路：攻击时移除敌人无敌帧</t>
+  </si>
+  <si>
+    <t>etstlib:anti_stun_glasses</t>
+  </si>
+  <si>
+    <t>防眩目镜：取消受伤时的屏幕抖动和视角场效果，免疫反胃</t>
+  </si>
+  <si>
+    <t>工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>护甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>etstlib:energy_shield</t>
+  </si>
+  <si>
+    <t>能量护盾：消耗FE格挡伤害，每10kFE格挡1伤害。若装备的当前电量无法完全格挡，则以一半的FE效率消耗全身带有此属性的装备的能量格挡</t>
+  </si>
+  <si>
+    <t>etstlib:clearing</t>
+  </si>
+  <si>
+    <t>洁净：免疫中毒和凋零效果</t>
+  </si>
+  <si>
+    <t>etstlib:momentum_accelerate</t>
+  </si>
+  <si>
+    <t>惯性加速：工具-20%攻击速度和挖掘速度，但是会随着使用变得更加趁手</t>
+  </si>
+  <si>
+    <t>etstlib:warp_attack</t>
+  </si>
+  <si>
+    <t>折跃攻击：当你未命中敌人时你会命中敌人</t>
+  </si>
+  <si>
+    <t>远程</t>
+  </si>
+  <si>
+    <t>远程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>etstlib:anisotropy</t>
+  </si>
+  <si>
+    <t>各向异性：增加工具全力打击时的伤害，减少不全力打击时的伤害，工具耐久越满这个效果越明显</t>
+  </si>
+  <si>
+    <t>etstlib:crystal_armor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晶质护甲：受伤时减少小于5点的伤害，增加大于5点的伤害</t>
+  </si>
+  <si>
+    <t>etstlib:reality_breaker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现实破坏者：使你的攻击穿透大部分原版防御手段</t>
+  </si>
+  <si>
+    <t>etstlib:glowing</t>
+  </si>
+  <si>
+    <t>外发光：装备时获得夜视效果，攻击/被攻击时高亮对方</t>
+  </si>
+  <si>
+    <t>etstlib:void_insight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚无之窥视：阻止大部分生物在你所在的世界生成</t>
+  </si>
+  <si>
+    <t>etstlib:global_traveler</t>
+  </si>
+  <si>
+    <t>环球旅行者：Shift-右键容器以绑定容器，此后工具的掉落物会存入其中。再次Shift-右键相同位置以解绑</t>
+  </si>
+  <si>
+    <t>etstlib:hardened</t>
+  </si>
+  <si>
+    <t>硬化：每级增加10%的耐久和伤害减免</t>
+  </si>
+  <si>
+    <t>etstlib:terrafirma</t>
+  </si>
+  <si>
+    <t>坚实基础：每秒给你恢复一定血量，等级越高效果越强</t>
+  </si>
+  <si>
+    <t>etstlib:fatal</t>
+  </si>
+  <si>
+    <t>致命创伤：遏制目标的生命恢复</t>
+  </si>
+  <si>
+    <t>etstlib:extra_dense</t>
+  </si>
+  <si>
+    <t>超级致密：工具具有更高的属性，但是变得更难修复</t>
+  </si>
+  <si>
+    <t>etstlib:inert_metal</t>
+  </si>
+  <si>
+    <t>惰性金属：每隔一段时间清除持有者身上的一个随机负面效果</t>
+  </si>
+  <si>
+    <t>etstlib:hyper_density</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>严丝合缝：你受到的伤害会额外被护甲值减免1次</t>
+  </si>
+  <si>
+    <t>etstlib:secondary_armor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>慎重的勇士：允许你的护甲格挡穿甲伤害</t>
+  </si>
+  <si>
+    <t>etstlib:resonating</t>
+  </si>
+  <si>
+    <t>稳态谐振：每隔一段时间，你会接收环境的声音，并根据声音的频率获得增益效果</t>
+  </si>
+  <si>
+    <t>辐射防护：每级提供10%的辐射防护</t>
+  </si>
+  <si>
+    <t>etstlib:radiation_shielding</t>
+  </si>
+  <si>
+    <t>辐射附加：全力打击时对目标施加100mSv辐射</t>
+  </si>
+  <si>
+    <t>etstlib:radiation_inflict</t>
+  </si>
+  <si>
+    <t>etstlib:applied_fixing</t>
+  </si>
+  <si>
+    <t>Fluix能量修复：置于AE2充能器中时缓缓修复自身</t>
+  </si>
+  <si>
+    <t>通用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>etstlib:energetic_attack</t>
+  </si>
+  <si>
+    <t>充能打击：全力打击时对目标施加少量魔法伤害</t>
+  </si>
+  <si>
+    <t>魔力修复：工具会缓慢消耗魔力修复自身</t>
+  </si>
+  <si>
+    <t>etstlib:mana_repair</t>
+  </si>
+  <si>
+    <t>泰拉射线：挥舞武器时，消耗魔力释放泰拉射线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>etstlib:terra_beam</t>
+  </si>
+  <si>
+    <t>etstlib:atomic_decompose</t>
+  </si>
+  <si>
+    <t>原子分解：你的挖掘速度固定为工具的挖掘速度，无视挖掘等级</t>
+  </si>
+  <si>
+    <t>粗鲁：对血量高于25的生物必定暴击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>etstlib:rude</t>
+  </si>
+  <si>
+    <t>刽子手：你的攻击无视敌人的无敌帧</t>
+  </si>
+  <si>
+    <t>etstlib:executioner</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:fragile</t>
+  </si>
+  <si>
+    <t>工具磨损时每级增加10%的概率额外消耗1点耐久</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:tetanus</t>
+  </si>
+  <si>
+    <t>对敌人施加破伤风效果，略微降低防御并使其受到的伤害增加20%</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:sculk_resonance</t>
+  </si>
+  <si>
+    <t>将工具造成的伤害转换为声波伤害</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:auto_shot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>让你的离子化射线炮在满蓄力时自动开火</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:annihilate</t>
+  </si>
+  <si>
+    <t>对你和目标同时造成等额爆炸伤害，随后造成不破坏地形的爆炸。你的攻击无视大部分原版防御手段</t>
+  </si>
+  <si>
+    <t>工具/远程？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tinkers_advanced:reactive_explosive_armor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少25%所受伤害并将伤害以爆炸的形式释放</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:sensor_interrupt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>极大降低怪物能感知到你的最大距离</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:metamorphium</t>
+  </si>
+  <si>
+    <t>每次磨损工具都有可能让它变得更加强力</t>
+  </si>
+  <si>
+    <t>通用？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tinkers_advanced:over_hold</t>
+  </si>
+  <si>
+    <t>+900%流体容量</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:flame_adaptive</t>
+  </si>
+  <si>
+    <t>装备后获得抗火效果，装备者着火时缓缓恢复耐久</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:supreme_density</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>令工具的部分攻击性属性额外生效多次</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:supreme_density_armor</t>
+  </si>
+  <si>
+    <t>护甲和护甲韧性翻倍，受击时80%的伤害会额外经历一次减伤计算</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:ionized</t>
+  </si>
+  <si>
+    <t>施加电离效果，持续造成伤害的同时降低敌人部分属性</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:disintegrate</t>
+  </si>
+  <si>
+    <t>随着挖掘的进行而无止尽地增加挖掘速度，但是耐久消耗也成倍增加</t>
+  </si>
+  <si>
+    <t>攻击时释放一道弧向敌人的脉冲</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:electric</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:echo_locating</t>
+  </si>
+  <si>
+    <t>工具会接收振动并标记产生振动的生物。攻击被标记的生物会施加额外的音爆伤害</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:elastic</t>
+  </si>
+  <si>
+    <t>工具损伤时，有概率不但不消耗耐久反而恢复耐久</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:shaping</t>
+  </si>
+  <si>
+    <t>随工具磨损而增加升级槽（于护甲则增加防御槽）</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:resonance_amplifier</t>
+  </si>
+  <si>
+    <t>每级增加10m射程</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:focusing_array</t>
+  </si>
+  <si>
+    <t>每级增加100%的流体效果作用半径</t>
+  </si>
+  <si>
+    <t>每级减少10%工具使用的流体</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:deep_catalysis</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:atom_grade</t>
+  </si>
+  <si>
+    <t>为工具增加一个防御槽或者升级槽，取决于工具类型</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:radioactive_armor</t>
+  </si>
+  <si>
+    <t>对攻击者施加100mSv辐射，每级获得25%辐射抗性</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:basalz_defense</t>
+  </si>
+  <si>
+    <t>每级护甲值、护甲韧性+1，获得爆裂抗性效果</t>
+  </si>
+  <si>
+    <t>全力打击时对目标施加割裂效果，减少目标护甲</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:basalz_inflict</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:blitz_defense</t>
+  </si>
+  <si>
+    <t>获得闪电抗性效果，被攻击时有5%概率闪避并电击攻击者</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:blitz_inflict</t>
+  </si>
+  <si>
+    <t>全力打击时释放弧向附近生物的脉冲，造成震荡效果</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:blizz_defense</t>
+  </si>
+  <si>
+    <t>获得冰霜抗性，冻结攻击者</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:blizz_inflict</t>
+  </si>
+  <si>
+    <t>攻击时冻结敌人，对着火的生物造成2倍伤害</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:flux_infused</t>
+  </si>
+  <si>
+    <t>每级获得1MFE的能量存储，工具使用时优先消耗能量存储而非耐久。按CoFH-循环模式键可以切换工具的模式</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:thermal_enhance</t>
+  </si>
+  <si>
+    <t>拥有石肤、碎裂、涌流、震荡、霜覆、坚冰、渴燃的全部属性</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:flux_arrow</t>
+  </si>
+  <si>
+    <t>激活模式下消耗能量存储凭空产生箭矢，箭矢基础伤害+1；注能模式下拉弓速度+50%，能产生药水箭，箭矢在击中时发生爆炸</t>
+  </si>
+  <si>
+    <t>+1时运、抢夺等级。激活模式下消耗能量增加挖掘速度并在攻击时附加4点穿甲伤害；注能模式下攻速+50%，挥舞时释放元素剑气</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:thermal_slash</t>
+  </si>
+  <si>
+    <t>tinkers_advanced:flux_defense</t>
+  </si>
+  <si>
+    <t>激活模式下有5%的概率消耗能量闪避伤害；注能模式下消耗能量抵消至多20%的伤害</t>
+  </si>
+  <si>
+    <t>tinkers_things:range</t>
+  </si>
+  <si>
+    <t>工具形制较长，能打击到远处的敌人</t>
+  </si>
+  <si>
+    <t>tinkers_things:fortified</t>
+  </si>
+  <si>
+    <t>提升工具基础数据和挖掘等级，并使其能用铜修复</t>
+  </si>
+  <si>
+    <t>tinkers_things:enhanced</t>
+  </si>
+  <si>
+    <t>“增强”需要“固化”作为前置</t>
+  </si>
+  <si>
+    <t>tinkers_things:blinding</t>
+  </si>
+  <si>
+    <t>箭矢能使目标暂时失明</t>
+  </si>
+  <si>
+    <t>tinkers_things:tracing</t>
+  </si>
+  <si>
+    <t>目标会发光数秒，方便追踪</t>
+  </si>
+  <si>
+    <t>tinkers_things:venom</t>
+  </si>
+  <si>
+    <t>目标会中毒，并持续受到伤害</t>
+  </si>
+  <si>
+    <t>tinkers_things:weakness</t>
+  </si>
+  <si>
+    <t>目标会暂时变得虚弱，其攻击伤害会降低</t>
+  </si>
+  <si>
+    <t>tinkers_things:stowing</t>
+  </si>
+  <si>
+    <t>工具额外获得9格储物槽位</t>
+  </si>
+  <si>
+    <t>tinkers_things:pouch</t>
+  </si>
+  <si>
+    <t>工具额外获得3格储物槽位</t>
+  </si>
+  <si>
+    <t>tinkers_things:hemodynamic</t>
+  </si>
+  <si>
+    <t>工具获得1个额外升级槽，但代价是什么？</t>
+  </si>
+  <si>
+    <t>tinkers_things:hemophobic</t>
+  </si>
+  <si>
+    <t>弹射物的精确度降低</t>
+  </si>
+  <si>
+    <t>tinkers_things:hemosistance</t>
+  </si>
+  <si>
+    <t>tinkers_things:silkitoxin</t>
+  </si>
+  <si>
+    <t>获得两个额外的防御槽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得两个额外的能力槽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tcintegrations:mana</t>
+  </si>
+  <si>
+    <t>如果物品栏内有能提供魔力的物品，拥有此强化的物品会以此修复自身。</t>
+  </si>
+  <si>
+    <t>tcintegrations:water_powered</t>
+  </si>
+  <si>
+    <t>在水中时，降低工具损耗耐久度的概率</t>
+  </si>
+  <si>
+    <t>tcintegrations:oxygenated</t>
+  </si>
+  <si>
+    <t>挖掘后给予短时间的氧气泡。</t>
+  </si>
+  <si>
+    <t>tcintegrations:soul_stained</t>
+  </si>
+  <si>
+    <t>盔甲获得保护屏障；工具和武器则能造成魔法伤害。</t>
+  </si>
+  <si>
+    <t>tcintegrations:kinetic</t>
+  </si>
+  <si>
+    <t>使用此工具会产生动能，并为物品栏中某一物品充能。</t>
+  </si>
+  <si>
+    <t>tcintegrations:dragonscales</t>
+  </si>
+  <si>
+    <t>增加抵御龙息攻击的保护。</t>
+  </si>
+  <si>
+    <t>tconstruct:cultivated</t>
+  </si>
+  <si>
+    <t>工具在修復時，單位材料能夠提供更多耐久度</t>
+  </si>
+  <si>
+    <t>tconstruct:stringy</t>
+  </si>
+  <si>
+    <t>工具可用線進行修復</t>
+  </si>
+  <si>
+    <t>tconstruct:unburdened</t>
+  </si>
+  <si>
+    <t>使用物品时移动速度受到的影响更小</t>
+  </si>
+  <si>
+    <t>tconstruct:depth_protection</t>
+  </si>
+  <si>
+    <t>tconstruct:enderference</t>
+  </si>
+  <si>
+    <t>暫時抑制終界使者的瞬移</t>
+  </si>
+  <si>
+    <t>tconstruct:overgrowth</t>
+  </si>
+  <si>
+    <t>工具隨著時間的推移會積累更多的過量史萊姆</t>
+  </si>
+  <si>
+    <t>tconstruct:searing</t>
+  </si>
+  <si>
+    <t>挖掘能在冶煉爐中熔化的方塊時，工具的挖掘速度更快</t>
+  </si>
+  <si>
+    <t>tconstruct:scorching</t>
+  </si>
+  <si>
+    <t>工具會對著火的目標造成額外傷害</t>
+  </si>
+  <si>
+    <t>tconstruct:dense</t>
+  </si>
+  <si>
+    <t>工具耐久更多，但是也越難修復</t>
+  </si>
+  <si>
+    <t>tconstruct:lustrous</t>
+  </si>
+  <si>
+    <t>開採的礦石掉落額外的金屬粒</t>
+  </si>
+  <si>
+    <t>tconstruct:sharpweight</t>
+  </si>
+  <si>
+    <t>挖掘速度更快，但是移動變得更加困難</t>
+  </si>
+  <si>
+    <t>tconstruct:heavy</t>
+  </si>
+  <si>
+    <t>持握時減緩移動速度，但工具的重量也使其攻擊傷害得以增強</t>
+  </si>
+  <si>
+    <t>tconstruct:featherweight</t>
+  </si>
+  <si>
+    <t>工具更為輕便；拉弓速度和精確度更高</t>
+  </si>
+  <si>
+    <t>tconstruct:crumbling</t>
+  </si>
+  <si>
+    <t>能更快地破坏不需要工具的方块</t>
+  </si>
+  <si>
+    <t>tconstruct:lightweight</t>
+  </si>
+  <si>
+    <t>工具比看起来更轻，所以攻击和挖掘更快，发射的投射物也更快</t>
+  </si>
+  <si>
+    <t>tconstruct:maintained</t>
+  </si>
+  <si>
+    <t>耐久度越高，工具的挖掘速度越快</t>
+  </si>
+  <si>
+    <t>tconstruct:ductile</t>
+  </si>
+  <si>
+    <t>工具更加耐用，挖掘速度更快，傷害更高</t>
+  </si>
+  <si>
+    <t>tconstruct:overlord</t>
+  </si>
+  <si>
+    <t>工具將部分耐久度轉化為新的過量史萊姆僕從</t>
+  </si>
+  <si>
+    <t>工具/远程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在低海拔时提升保护，每低于海平面64格，保护+5%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1143,6 +1817,15 @@
       <color theme="10"/>
       <name val="等线"/>
       <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1327,6 +2010,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1336,19 +2022,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1720,11 +2403,11 @@
       <c r="C6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="17"/>
-      <c r="G6" s="16"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="17"/>
       <c r="L6" s="6" t="s">
         <v>4</v>
       </c>
@@ -1848,23 +2531,23 @@
       <c r="R13" s="2"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="16"/>
-      <c r="L14" s="15" t="s">
+      <c r="F14" s="17"/>
+      <c r="L14" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="16"/>
+      <c r="M14" s="17"/>
       <c r="N14" s="6"/>
       <c r="O14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P14" s="6"/>
-      <c r="Q14" s="15" t="s">
+      <c r="Q14" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="R14" s="16"/>
+      <c r="R14" s="17"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E15" s="2" t="s">
@@ -1979,18 +2662,18 @@
       <c r="V21" s="2"/>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F22" s="16"/>
+      <c r="F22" s="17"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="L22" s="15" t="s">
+      <c r="L22" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="M22" s="16"/>
+      <c r="M22" s="17"/>
       <c r="N22" s="6"/>
       <c r="O22" s="13" t="s">
         <v>41</v>
@@ -2000,12 +2683,12 @@
         <v>16</v>
       </c>
       <c r="R22" s="13"/>
-      <c r="S22" s="15" t="s">
+      <c r="S22" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="T22" s="17"/>
-      <c r="U22" s="17"/>
-      <c r="V22" s="16"/>
+      <c r="T22" s="18"/>
+      <c r="U22" s="18"/>
+      <c r="V22" s="17"/>
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.2">
       <c r="E23" s="2"/>
@@ -2063,10 +2746,10 @@
       <c r="S24" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="T24" s="22" t="s">
+      <c r="T24" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="U24" s="22" t="s">
+      <c r="U24" s="2" t="s">
         <v>257</v>
       </c>
       <c r="V24" s="2"/>
@@ -2396,15 +3079,15 @@
         <v>204</v>
       </c>
       <c r="S41" s="6"/>
-      <c r="T41" s="15" t="s">
+      <c r="T41" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="U41" s="16"/>
+      <c r="U41" s="17"/>
       <c r="V41" s="14"/>
-      <c r="W41" s="15" t="s">
+      <c r="W41" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="X41" s="16"/>
+      <c r="X41" s="17"/>
       <c r="Y41" s="13"/>
       <c r="Z41" s="13" t="s">
         <v>210</v>
@@ -2681,45 +3364,45 @@
       <c r="I3" s="19"/>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="18"/>
-      <c r="M5" s="18" t="s">
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="N5" s="18"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="18"/>
-      <c r="R5" s="18"/>
-      <c r="S5" s="18"/>
-      <c r="T5" s="18"/>
-      <c r="U5" s="18"/>
-      <c r="V5" s="18" t="s">
+      <c r="N5" s="21"/>
+      <c r="O5" s="21"/>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="21"/>
+      <c r="R5" s="21"/>
+      <c r="S5" s="21"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="21"/>
+      <c r="V5" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="W5" s="18"/>
-      <c r="X5" s="18" t="s">
+      <c r="W5" s="21"/>
+      <c r="X5" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="Y5" s="18"/>
-      <c r="Z5" s="18"/>
-      <c r="AA5" s="18"/>
-      <c r="AB5" s="18"/>
-      <c r="AC5" s="18"/>
-      <c r="AD5" s="18"/>
-      <c r="AE5" s="18"/>
-      <c r="AF5" s="18"/>
-      <c r="AG5" s="18"/>
+      <c r="Y5" s="21"/>
+      <c r="Z5" s="21"/>
+      <c r="AA5" s="21"/>
+      <c r="AB5" s="21"/>
+      <c r="AC5" s="21"/>
+      <c r="AD5" s="21"/>
+      <c r="AE5" s="21"/>
+      <c r="AF5" s="21"/>
+      <c r="AG5" s="21"/>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C6" s="4" t="s">
@@ -3914,10 +4597,10 @@
       <c r="E33" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="F33" s="21" t="s">
+      <c r="F33" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="G33" s="21" t="s">
+      <c r="G33" s="15" t="s">
         <v>222</v>
       </c>
     </row>
@@ -4028,14 +4711,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="X5:AG5"/>
+    <mergeCell ref="V5:W5"/>
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="C2:E3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="M5:U5"/>
     <mergeCell ref="G2:I3"/>
-    <mergeCell ref="X5:AG5"/>
-    <mergeCell ref="V5:W5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4045,69 +4728,1228 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A68B449-6496-4C27-B0D0-42A49C13CB56}">
-  <dimension ref="A2:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="C2:E116"/>
+  <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="41.375" customWidth="1"/>
+    <col min="5" max="5" width="68.125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C2" t="s">
         <v>174</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C3" t="s">
         <v>175</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="4" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C4" t="s">
         <v>176</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6">
+    <row r="6" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C6">
         <v>1</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7">
+    <row r="7" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C7">
         <v>2</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>218</v>
+      </c>
+    </row>
+    <row r="12" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C12" t="s">
+        <v>286</v>
+      </c>
+      <c r="D12" t="s">
+        <v>272</v>
+      </c>
+      <c r="E12" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C13" t="s">
+        <v>286</v>
+      </c>
+      <c r="D13" t="s">
+        <v>274</v>
+      </c>
+      <c r="E13" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="14" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C14" t="s">
+        <v>286</v>
+      </c>
+      <c r="D14" t="s">
+        <v>276</v>
+      </c>
+      <c r="E14" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="15" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C15" t="s">
+        <v>297</v>
+      </c>
+      <c r="D15" t="s">
+        <v>278</v>
+      </c>
+      <c r="E15" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="16" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C16" t="s">
+        <v>286</v>
+      </c>
+      <c r="D16" t="s">
+        <v>280</v>
+      </c>
+      <c r="E16" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C17" t="s">
+        <v>286</v>
+      </c>
+      <c r="D17" t="s">
+        <v>282</v>
+      </c>
+      <c r="E17" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C18" t="s">
+        <v>287</v>
+      </c>
+      <c r="D18" t="s">
+        <v>284</v>
+      </c>
+      <c r="E18" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C19" t="s">
+        <v>287</v>
+      </c>
+      <c r="D19" t="s">
+        <v>288</v>
+      </c>
+      <c r="E19" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C20" t="s">
+        <v>287</v>
+      </c>
+      <c r="D20" t="s">
+        <v>290</v>
+      </c>
+      <c r="E20" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C21" t="s">
+        <v>286</v>
+      </c>
+      <c r="D21" t="s">
+        <v>292</v>
+      </c>
+      <c r="E21" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="22" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C22" t="s">
+        <v>297</v>
+      </c>
+      <c r="D22" t="s">
+        <v>294</v>
+      </c>
+      <c r="E22" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="23" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C23" t="s">
+        <v>286</v>
+      </c>
+      <c r="D23" t="s">
+        <v>298</v>
+      </c>
+      <c r="E23" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="24" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C24" t="s">
+        <v>287</v>
+      </c>
+      <c r="D24" t="s">
+        <v>300</v>
+      </c>
+      <c r="E24" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="25" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C25" t="s">
+        <v>286</v>
+      </c>
+      <c r="D25" t="s">
+        <v>302</v>
+      </c>
+      <c r="E25" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="26" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C26" t="s">
+        <v>287</v>
+      </c>
+      <c r="D26" t="s">
+        <v>304</v>
+      </c>
+      <c r="E26" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="27" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C27" t="s">
+        <v>287</v>
+      </c>
+      <c r="D27" t="s">
+        <v>306</v>
+      </c>
+      <c r="E27" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="28" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C28" t="s">
+        <v>286</v>
+      </c>
+      <c r="D28" t="s">
+        <v>308</v>
+      </c>
+      <c r="E28" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="29" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C29" t="s">
+        <v>287</v>
+      </c>
+      <c r="D29" t="s">
+        <v>310</v>
+      </c>
+      <c r="E29" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="30" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C30" t="s">
+        <v>287</v>
+      </c>
+      <c r="D30" t="s">
+        <v>312</v>
+      </c>
+      <c r="E30" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="31" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C31" t="s">
+        <v>286</v>
+      </c>
+      <c r="D31" t="s">
+        <v>314</v>
+      </c>
+      <c r="E31" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="32" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C32" t="s">
+        <v>332</v>
+      </c>
+      <c r="D32" t="s">
+        <v>316</v>
+      </c>
+      <c r="E32" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="33" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C33" t="s">
+        <v>287</v>
+      </c>
+      <c r="D33" t="s">
+        <v>318</v>
+      </c>
+      <c r="E33" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C34" t="s">
+        <v>287</v>
+      </c>
+      <c r="D34" t="s">
+        <v>320</v>
+      </c>
+      <c r="E34" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C35" t="s">
+        <v>287</v>
+      </c>
+      <c r="D35" t="s">
+        <v>322</v>
+      </c>
+      <c r="E35" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="36" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C36" t="s">
+        <v>287</v>
+      </c>
+      <c r="D36" t="s">
+        <v>324</v>
+      </c>
+      <c r="E36" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="37" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C37" t="s">
+        <v>287</v>
+      </c>
+      <c r="D37" t="s">
+        <v>327</v>
+      </c>
+      <c r="E37" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="38" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C38" t="s">
+        <v>286</v>
+      </c>
+      <c r="D38" t="s">
+        <v>329</v>
+      </c>
+      <c r="E38" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="39" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C39" t="s">
+        <v>332</v>
+      </c>
+      <c r="D39" t="s">
+        <v>330</v>
+      </c>
+      <c r="E39" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="40" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C40" t="s">
+        <v>286</v>
+      </c>
+      <c r="D40" t="s">
+        <v>333</v>
+      </c>
+      <c r="E40" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="41" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C41" t="s">
+        <v>332</v>
+      </c>
+      <c r="D41" t="s">
+        <v>336</v>
+      </c>
+      <c r="E41" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="42" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C42" t="s">
+        <v>286</v>
+      </c>
+      <c r="D42" t="s">
+        <v>338</v>
+      </c>
+      <c r="E42" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="43" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C43" t="s">
+        <v>286</v>
+      </c>
+      <c r="D43" t="s">
+        <v>339</v>
+      </c>
+      <c r="E43" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="44" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C44" t="s">
+        <v>286</v>
+      </c>
+      <c r="D44" t="s">
+        <v>342</v>
+      </c>
+      <c r="E44" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="45" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C45" t="s">
+        <v>286</v>
+      </c>
+      <c r="D45" t="s">
+        <v>344</v>
+      </c>
+      <c r="E45" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="46" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C46" t="s">
+        <v>332</v>
+      </c>
+      <c r="D46" s="22" t="s">
+        <v>345</v>
+      </c>
+      <c r="E46" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="47" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C47" t="s">
+        <v>355</v>
+      </c>
+      <c r="D47" s="22" t="s">
+        <v>347</v>
+      </c>
+      <c r="E47" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="48" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C48" t="s">
+        <v>355</v>
+      </c>
+      <c r="D48" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="E48" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="49" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C49" t="s">
+        <v>297</v>
+      </c>
+      <c r="D49" s="22" t="s">
+        <v>351</v>
+      </c>
+      <c r="E49" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="50" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C50" t="s">
+        <v>355</v>
+      </c>
+      <c r="D50" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="E50" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="51" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C51" t="s">
+        <v>287</v>
+      </c>
+      <c r="D51" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="E51" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="52" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C52" t="s">
+        <v>287</v>
+      </c>
+      <c r="D52" s="22" t="s">
+        <v>358</v>
+      </c>
+      <c r="E52" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="53" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C53" t="s">
+        <v>362</v>
+      </c>
+      <c r="D53" s="22" t="s">
+        <v>360</v>
+      </c>
+      <c r="E53" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="54" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C54" t="s">
+        <v>332</v>
+      </c>
+      <c r="D54" s="22" t="s">
+        <v>363</v>
+      </c>
+      <c r="E54" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="55" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C55" t="s">
+        <v>287</v>
+      </c>
+      <c r="D55" s="22" t="s">
+        <v>365</v>
+      </c>
+      <c r="E55" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="56" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C56" t="s">
+        <v>355</v>
+      </c>
+      <c r="D56" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="E56" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="57" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C57" t="s">
+        <v>287</v>
+      </c>
+      <c r="D57" s="22" t="s">
+        <v>369</v>
+      </c>
+      <c r="E57" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="58" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C58" t="s">
+        <v>355</v>
+      </c>
+      <c r="D58" s="22" t="s">
+        <v>371</v>
+      </c>
+      <c r="E58" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="59" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C59" t="s">
+        <v>286</v>
+      </c>
+      <c r="D59" s="22" t="s">
+        <v>373</v>
+      </c>
+      <c r="E59" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="60" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C60" t="s">
+        <v>355</v>
+      </c>
+      <c r="D60" s="22" t="s">
+        <v>376</v>
+      </c>
+      <c r="E60" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="61" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C61" t="s">
+        <v>355</v>
+      </c>
+      <c r="D61" s="22" t="s">
+        <v>377</v>
+      </c>
+      <c r="E61" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="62" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C62" t="s">
+        <v>332</v>
+      </c>
+      <c r="D62" s="22" t="s">
+        <v>379</v>
+      </c>
+      <c r="E62" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="63" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C63" t="s">
+        <v>332</v>
+      </c>
+      <c r="D63" s="22" t="s">
+        <v>381</v>
+      </c>
+      <c r="E63" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="64" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C64" t="s">
+        <v>296</v>
+      </c>
+      <c r="D64" s="22" t="s">
+        <v>383</v>
+      </c>
+      <c r="E64" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="65" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C65" t="s">
+        <v>296</v>
+      </c>
+      <c r="D65" s="22" t="s">
+        <v>385</v>
+      </c>
+      <c r="E65" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="66" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C66" t="s">
+        <v>332</v>
+      </c>
+      <c r="D66" s="22" t="s">
+        <v>388</v>
+      </c>
+      <c r="E66" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="67" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C67" t="s">
+        <v>332</v>
+      </c>
+      <c r="D67" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="E67" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="68" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C68" t="s">
+        <v>287</v>
+      </c>
+      <c r="D68" s="22" t="s">
+        <v>391</v>
+      </c>
+      <c r="E68" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="69" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C69" t="s">
+        <v>287</v>
+      </c>
+      <c r="D69" s="22" t="s">
+        <v>393</v>
+      </c>
+      <c r="E69" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="70" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C70" t="s">
+        <v>286</v>
+      </c>
+      <c r="D70" s="22" t="s">
+        <v>396</v>
+      </c>
+      <c r="E70" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="71" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C71" t="s">
+        <v>287</v>
+      </c>
+      <c r="D71" s="22" t="s">
+        <v>397</v>
+      </c>
+      <c r="E71" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="72" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C72" t="s">
+        <v>286</v>
+      </c>
+      <c r="D72" s="22" t="s">
+        <v>399</v>
+      </c>
+      <c r="E72" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="73" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C73" t="s">
+        <v>287</v>
+      </c>
+      <c r="D73" s="22" t="s">
+        <v>401</v>
+      </c>
+      <c r="E73" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="74" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C74" t="s">
+        <v>286</v>
+      </c>
+      <c r="D74" s="22" t="s">
+        <v>403</v>
+      </c>
+      <c r="E74" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="75" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C75" t="s">
+        <v>332</v>
+      </c>
+      <c r="D75" s="22" t="s">
+        <v>405</v>
+      </c>
+      <c r="E75" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="76" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C76" t="s">
+        <v>332</v>
+      </c>
+      <c r="D76" s="22" t="s">
+        <v>407</v>
+      </c>
+      <c r="E76" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="77" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C77" t="s">
+        <v>297</v>
+      </c>
+      <c r="D77" s="22" t="s">
+        <v>409</v>
+      </c>
+      <c r="E77" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="78" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C78" t="s">
+        <v>286</v>
+      </c>
+      <c r="D78" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="E78" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="79" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C79" t="s">
+        <v>287</v>
+      </c>
+      <c r="D79" s="22" t="s">
+        <v>413</v>
+      </c>
+      <c r="E79" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="80" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C80" t="s">
+        <v>286</v>
+      </c>
+      <c r="D80" t="s">
+        <v>415</v>
+      </c>
+      <c r="E80" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="81" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C81" t="s">
+        <v>286</v>
+      </c>
+      <c r="D81" t="s">
+        <v>417</v>
+      </c>
+      <c r="E81" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="82" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C82" t="s">
+        <v>332</v>
+      </c>
+      <c r="D82" t="s">
+        <v>419</v>
+      </c>
+      <c r="E82" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="83" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C83" t="s">
+        <v>296</v>
+      </c>
+      <c r="D83" t="s">
+        <v>421</v>
+      </c>
+      <c r="E83" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="84" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C84" t="s">
+        <v>286</v>
+      </c>
+      <c r="D84" t="s">
+        <v>423</v>
+      </c>
+      <c r="E84" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="85" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C85" t="s">
+        <v>286</v>
+      </c>
+      <c r="D85" t="s">
+        <v>425</v>
+      </c>
+      <c r="E85" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="86" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C86" t="s">
+        <v>286</v>
+      </c>
+      <c r="D86" t="s">
+        <v>427</v>
+      </c>
+      <c r="E86" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="87" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C87" t="s">
+        <v>286</v>
+      </c>
+      <c r="D87" t="s">
+        <v>429</v>
+      </c>
+      <c r="E87" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="88" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C88" t="s">
+        <v>286</v>
+      </c>
+      <c r="D88" t="s">
+        <v>431</v>
+      </c>
+      <c r="E88" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="89" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C89" t="s">
+        <v>286</v>
+      </c>
+      <c r="D89" t="s">
+        <v>433</v>
+      </c>
+      <c r="E89" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="90" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C90" t="s">
+        <v>296</v>
+      </c>
+      <c r="D90" t="s">
+        <v>435</v>
+      </c>
+      <c r="E90" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="91" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C91" t="s">
+        <v>287</v>
+      </c>
+      <c r="D91" t="s">
+        <v>437</v>
+      </c>
+      <c r="E91" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="92" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C92" t="s">
+        <v>286</v>
+      </c>
+      <c r="D92" t="s">
+        <v>438</v>
+      </c>
+      <c r="E92" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="93" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C93" t="s">
+        <v>332</v>
+      </c>
+      <c r="D93" t="s">
+        <v>441</v>
+      </c>
+      <c r="E93" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="94" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C94" t="s">
+        <v>286</v>
+      </c>
+      <c r="D94" t="s">
+        <v>443</v>
+      </c>
+      <c r="E94" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="95" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C95" t="s">
+        <v>286</v>
+      </c>
+      <c r="D95" t="s">
+        <v>445</v>
+      </c>
+      <c r="E95" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="96" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C96" t="s">
+        <v>286</v>
+      </c>
+      <c r="D96" t="s">
+        <v>447</v>
+      </c>
+      <c r="E96" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="97" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C97" t="s">
+        <v>286</v>
+      </c>
+      <c r="D97" t="s">
+        <v>449</v>
+      </c>
+      <c r="E97" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="98" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C98" t="s">
+        <v>287</v>
+      </c>
+      <c r="D98" t="s">
+        <v>451</v>
+      </c>
+      <c r="E98" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="99" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C99" t="s">
+        <v>332</v>
+      </c>
+      <c r="D99" t="s">
+        <v>453</v>
+      </c>
+      <c r="E99" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="100" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C100" t="s">
+        <v>332</v>
+      </c>
+      <c r="D100" t="s">
+        <v>455</v>
+      </c>
+      <c r="E100" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="101" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C101" t="s">
+        <v>286</v>
+      </c>
+      <c r="D101" t="s">
+        <v>457</v>
+      </c>
+      <c r="E101" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="102" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C102" t="s">
+        <v>287</v>
+      </c>
+      <c r="D102" t="s">
+        <v>459</v>
+      </c>
+      <c r="E102" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="103" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C103" t="s">
+        <v>286</v>
+      </c>
+      <c r="D103" t="s">
+        <v>460</v>
+      </c>
+      <c r="E103" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="104" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C104" t="s">
+        <v>332</v>
+      </c>
+      <c r="D104" t="s">
+        <v>462</v>
+      </c>
+      <c r="E104" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="105" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C105" t="s">
+        <v>286</v>
+      </c>
+      <c r="D105" t="s">
+        <v>464</v>
+      </c>
+      <c r="E105" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="106" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C106" t="s">
+        <v>286</v>
+      </c>
+      <c r="D106" t="s">
+        <v>466</v>
+      </c>
+      <c r="E106" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="107" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C107" t="s">
+        <v>332</v>
+      </c>
+      <c r="D107" t="s">
+        <v>468</v>
+      </c>
+      <c r="E107" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="108" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C108" t="s">
+        <v>286</v>
+      </c>
+      <c r="D108" t="s">
+        <v>470</v>
+      </c>
+      <c r="E108" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="109" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C109" t="s">
+        <v>286</v>
+      </c>
+      <c r="D109" t="s">
+        <v>472</v>
+      </c>
+      <c r="E109" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="110" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C110" t="s">
+        <v>286</v>
+      </c>
+      <c r="D110" t="s">
+        <v>474</v>
+      </c>
+      <c r="E110" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="111" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C111" t="s">
+        <v>488</v>
+      </c>
+      <c r="D111" t="s">
+        <v>476</v>
+      </c>
+      <c r="E111" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="112" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C112" t="s">
+        <v>286</v>
+      </c>
+      <c r="D112" t="s">
+        <v>478</v>
+      </c>
+      <c r="E112" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="113" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C113" t="s">
+        <v>332</v>
+      </c>
+      <c r="D113" t="s">
+        <v>480</v>
+      </c>
+      <c r="E113" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="114" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C114" t="s">
+        <v>286</v>
+      </c>
+      <c r="D114" t="s">
+        <v>482</v>
+      </c>
+      <c r="E114" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="115" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C115" t="s">
+        <v>286</v>
+      </c>
+      <c r="D115" t="s">
+        <v>484</v>
+      </c>
+      <c r="E115" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="116" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C116" t="s">
+        <v>332</v>
+      </c>
+      <c r="D116" t="s">
+        <v>486</v>
+      </c>
+      <c r="E116" t="s">
+        <v>487</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{0D12EE59-3D1E-41EA-A0FB-D93025F5F202}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{59A4AEFA-CDF7-40FE-99CD-0F054CEE697C}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{83E855DC-B61A-4DA3-894B-4E2E2430F18C}"/>
-    <hyperlink ref="C2" r:id="rId4" xr:uid="{D769C703-F075-4BC2-BFCF-813F6269BED3}"/>
-    <hyperlink ref="C3" r:id="rId5" xr:uid="{B9922A97-5881-49A0-82E9-7D2182B37711}"/>
-    <hyperlink ref="C4" r:id="rId6" xr:uid="{ECDF5B2F-9405-4D5F-BCF0-0C500B63DD84}"/>
-    <hyperlink ref="B6" r:id="rId7" xr:uid="{670D1826-5831-45ED-B48D-0F99BD8558ED}"/>
-    <hyperlink ref="B7" r:id="rId8" xr:uid="{F5948949-146C-4F7F-9E00-9192B6631811}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{0D12EE59-3D1E-41EA-A0FB-D93025F5F202}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{59A4AEFA-CDF7-40FE-99CD-0F054CEE697C}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{83E855DC-B61A-4DA3-894B-4E2E2430F18C}"/>
+    <hyperlink ref="E2" r:id="rId4" xr:uid="{D769C703-F075-4BC2-BFCF-813F6269BED3}"/>
+    <hyperlink ref="E3" r:id="rId5" xr:uid="{B9922A97-5881-49A0-82E9-7D2182B37711}"/>
+    <hyperlink ref="E4" r:id="rId6" xr:uid="{ECDF5B2F-9405-4D5F-BCF0-0C500B63DD84}"/>
+    <hyperlink ref="D6" r:id="rId7" xr:uid="{670D1826-5831-45ED-B48D-0F99BD8558ED}"/>
+    <hyperlink ref="D7" r:id="rId8" xr:uid="{F5948949-146C-4F7F-9E00-9192B6631811}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>

--- a/dev_stuffs/palmon.xlsx
+++ b/dev_stuffs/palmon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\Palmon\dev_stuffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF999414-7514-47EB-9BB7-63A45EE0B884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5991219-BD7F-4ABB-9E9C-7C0964B894D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15735" yWindow="4605" windowWidth="23940" windowHeight="15435" activeTab="2" xr2:uid="{41DCFB66-B5C9-4783-B084-0F93150E63F9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{41DCFB66-B5C9-4783-B084-0F93150E63F9}"/>
   </bookViews>
   <sheets>
     <sheet name="材料" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="493">
   <si>
     <t>阶段1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1781,6 +1781,18 @@
   </si>
   <si>
     <t>在低海拔时提升保护，每低于海平面64格，保护+5%</t>
+  </si>
+  <si>
+    <t>精炼钢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精炼M钢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚合物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1964,7 +1976,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2013,6 +2025,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2022,17 +2037,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2403,11 +2418,11 @@
       <c r="C6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="17"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="18"/>
       <c r="L6" s="6" t="s">
         <v>4</v>
       </c>
@@ -2531,23 +2546,23 @@
       <c r="R13" s="2"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="17"/>
-      <c r="L14" s="16" t="s">
+      <c r="F14" s="18"/>
+      <c r="L14" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="17"/>
+      <c r="M14" s="18"/>
       <c r="N14" s="6"/>
       <c r="O14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P14" s="6"/>
-      <c r="Q14" s="16" t="s">
+      <c r="Q14" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="R14" s="17"/>
+      <c r="R14" s="18"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E15" s="2" t="s">
@@ -2585,7 +2600,7 @@
       </c>
       <c r="R16" s="2"/>
     </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:23" x14ac:dyDescent="0.2">
       <c r="E17" s="2" t="s">
         <v>19</v>
       </c>
@@ -2604,7 +2619,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:23" x14ac:dyDescent="0.2">
       <c r="E18" s="2" t="s">
         <v>23</v>
       </c>
@@ -2621,17 +2636,17 @@
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
     </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:23" x14ac:dyDescent="0.2">
       <c r="T19" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:23" x14ac:dyDescent="0.2">
       <c r="E20" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>43</v>
       </c>
@@ -2660,20 +2675,21 @@
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
       <c r="V21" s="2"/>
-    </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="E22" s="16" t="s">
+      <c r="W21" s="2"/>
+    </row>
+    <row r="22" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="E22" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="F22" s="17"/>
+      <c r="F22" s="18"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="L22" s="16" t="s">
+      <c r="L22" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="M22" s="17"/>
+      <c r="M22" s="18"/>
       <c r="N22" s="6"/>
       <c r="O22" s="13" t="s">
         <v>41</v>
@@ -2683,14 +2699,15 @@
         <v>16</v>
       </c>
       <c r="R22" s="13"/>
-      <c r="S22" s="16" t="s">
+      <c r="S22" s="23" t="s">
         <v>210</v>
       </c>
-      <c r="T22" s="18"/>
-      <c r="U22" s="18"/>
-      <c r="V22" s="17"/>
-    </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="T22" s="23"/>
+      <c r="U22" s="23"/>
+      <c r="V22" s="23"/>
+      <c r="W22" s="23"/>
+    </row>
+    <row r="23" spans="2:23" x14ac:dyDescent="0.2">
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -2716,14 +2733,14 @@
       <c r="T23" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="U23" s="2" t="s">
+      <c r="V23" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="V23" s="2" t="s">
+      <c r="W23" s="2" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:23" x14ac:dyDescent="0.2">
       <c r="E24" s="2" t="s">
         <v>249</v>
       </c>
@@ -2750,11 +2767,13 @@
         <v>256</v>
       </c>
       <c r="U24" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="W24" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="V24" s="2"/>
-    </row>
-    <row r="25" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="2:23" x14ac:dyDescent="0.2">
       <c r="E25" s="2" t="s">
         <v>33</v>
       </c>
@@ -2775,10 +2794,16 @@
       <c r="S25" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="U25" s="2"/>
-      <c r="V25" s="2"/>
-    </row>
-    <row r="26" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="T25" s="2"/>
+      <c r="U25" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="V25" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="W25" s="2"/>
+    </row>
+    <row r="26" spans="2:23" x14ac:dyDescent="0.2">
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -2800,8 +2825,9 @@
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
       <c r="V26" s="2"/>
-    </row>
-    <row r="27" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="2"/>
+    </row>
+    <row r="27" spans="2:23" x14ac:dyDescent="0.2">
       <c r="E27" s="2" t="s">
         <v>50</v>
       </c>
@@ -2827,8 +2853,9 @@
       </c>
       <c r="U27" s="2"/>
       <c r="V27" s="2"/>
-    </row>
-    <row r="28" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="2"/>
+    </row>
+    <row r="28" spans="2:23" x14ac:dyDescent="0.2">
       <c r="L28" s="2" t="s">
         <v>73</v>
       </c>
@@ -2846,13 +2873,14 @@
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
-    </row>
-    <row r="30" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="2"/>
+    </row>
+    <row r="30" spans="2:23" x14ac:dyDescent="0.2">
       <c r="E30" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
         <v>52</v>
       </c>
@@ -2881,7 +2909,7 @@
       <c r="U31" s="2"/>
       <c r="V31" s="2"/>
     </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>54</v>
       </c>
@@ -3079,15 +3107,15 @@
         <v>204</v>
       </c>
       <c r="S41" s="6"/>
-      <c r="T41" s="16" t="s">
+      <c r="T41" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="U41" s="17"/>
+      <c r="U41" s="18"/>
       <c r="V41" s="14"/>
-      <c r="W41" s="16" t="s">
+      <c r="W41" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="X41" s="17"/>
+      <c r="X41" s="18"/>
       <c r="Y41" s="13"/>
       <c r="Z41" s="13" t="s">
         <v>210</v>
@@ -3327,7 +3355,7 @@
     <mergeCell ref="L14:M14"/>
     <mergeCell ref="T41:U41"/>
     <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="S22:V22"/>
+    <mergeCell ref="S22:W22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3344,65 +3372,65 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="G2" s="19" t="s">
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="G2" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21" t="s">
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="N5" s="21"/>
-      <c r="O5" s="21"/>
-      <c r="P5" s="21"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="21"/>
-      <c r="S5" s="21"/>
-      <c r="T5" s="21"/>
-      <c r="U5" s="21"/>
-      <c r="V5" s="21" t="s">
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="W5" s="21"/>
-      <c r="X5" s="21" t="s">
+      <c r="W5" s="20"/>
+      <c r="X5" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="Y5" s="21"/>
-      <c r="Z5" s="21"/>
-      <c r="AA5" s="21"/>
-      <c r="AB5" s="21"/>
-      <c r="AC5" s="21"/>
-      <c r="AD5" s="21"/>
-      <c r="AE5" s="21"/>
-      <c r="AF5" s="21"/>
-      <c r="AG5" s="21"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="20"/>
+      <c r="AA5" s="20"/>
+      <c r="AB5" s="20"/>
+      <c r="AC5" s="20"/>
+      <c r="AD5" s="20"/>
+      <c r="AE5" s="20"/>
+      <c r="AF5" s="20"/>
+      <c r="AG5" s="20"/>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C6" s="4" t="s">
@@ -3500,7 +3528,7 @@
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="21" t="s">
         <v>78</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -3598,7 +3626,7 @@
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B8" s="19"/>
+      <c r="B8" s="21"/>
       <c r="C8" s="4" t="s">
         <v>84</v>
       </c>
@@ -3664,7 +3692,7 @@
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B9" s="19"/>
+      <c r="B9" s="21"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -3700,7 +3728,7 @@
       <c r="AG9" s="4"/>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="21" t="s">
         <v>79</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -3796,7 +3824,7 @@
       <c r="AG10" s="4"/>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B11" s="19"/>
+      <c r="B11" s="21"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4" t="s">
         <v>91</v>
@@ -3860,7 +3888,7 @@
       <c r="AG11" s="4"/>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B12" s="19"/>
+      <c r="B12" s="21"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -3900,7 +3928,7 @@
       <c r="AG12" s="4"/>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B13" s="19"/>
+      <c r="B13" s="21"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -5162,7 +5190,7 @@
       <c r="C46" t="s">
         <v>332</v>
       </c>
-      <c r="D46" s="22" t="s">
+      <c r="D46" s="16" t="s">
         <v>345</v>
       </c>
       <c r="E46" t="s">
@@ -5173,7 +5201,7 @@
       <c r="C47" t="s">
         <v>355</v>
       </c>
-      <c r="D47" s="22" t="s">
+      <c r="D47" s="16" t="s">
         <v>347</v>
       </c>
       <c r="E47" t="s">
@@ -5184,7 +5212,7 @@
       <c r="C48" t="s">
         <v>355</v>
       </c>
-      <c r="D48" s="22" t="s">
+      <c r="D48" s="16" t="s">
         <v>349</v>
       </c>
       <c r="E48" t="s">
@@ -5195,7 +5223,7 @@
       <c r="C49" t="s">
         <v>297</v>
       </c>
-      <c r="D49" s="22" t="s">
+      <c r="D49" s="16" t="s">
         <v>351</v>
       </c>
       <c r="E49" t="s">
@@ -5206,7 +5234,7 @@
       <c r="C50" t="s">
         <v>355</v>
       </c>
-      <c r="D50" s="22" t="s">
+      <c r="D50" s="16" t="s">
         <v>353</v>
       </c>
       <c r="E50" t="s">
@@ -5217,7 +5245,7 @@
       <c r="C51" t="s">
         <v>287</v>
       </c>
-      <c r="D51" s="22" t="s">
+      <c r="D51" s="16" t="s">
         <v>356</v>
       </c>
       <c r="E51" t="s">
@@ -5228,7 +5256,7 @@
       <c r="C52" t="s">
         <v>287</v>
       </c>
-      <c r="D52" s="22" t="s">
+      <c r="D52" s="16" t="s">
         <v>358</v>
       </c>
       <c r="E52" t="s">
@@ -5239,7 +5267,7 @@
       <c r="C53" t="s">
         <v>362</v>
       </c>
-      <c r="D53" s="22" t="s">
+      <c r="D53" s="16" t="s">
         <v>360</v>
       </c>
       <c r="E53" t="s">
@@ -5250,7 +5278,7 @@
       <c r="C54" t="s">
         <v>332</v>
       </c>
-      <c r="D54" s="22" t="s">
+      <c r="D54" s="16" t="s">
         <v>363</v>
       </c>
       <c r="E54" t="s">
@@ -5261,7 +5289,7 @@
       <c r="C55" t="s">
         <v>287</v>
       </c>
-      <c r="D55" s="22" t="s">
+      <c r="D55" s="16" t="s">
         <v>365</v>
       </c>
       <c r="E55" t="s">
@@ -5272,7 +5300,7 @@
       <c r="C56" t="s">
         <v>355</v>
       </c>
-      <c r="D56" s="22" t="s">
+      <c r="D56" s="16" t="s">
         <v>367</v>
       </c>
       <c r="E56" t="s">
@@ -5283,7 +5311,7 @@
       <c r="C57" t="s">
         <v>287</v>
       </c>
-      <c r="D57" s="22" t="s">
+      <c r="D57" s="16" t="s">
         <v>369</v>
       </c>
       <c r="E57" t="s">
@@ -5294,7 +5322,7 @@
       <c r="C58" t="s">
         <v>355</v>
       </c>
-      <c r="D58" s="22" t="s">
+      <c r="D58" s="16" t="s">
         <v>371</v>
       </c>
       <c r="E58" t="s">
@@ -5305,7 +5333,7 @@
       <c r="C59" t="s">
         <v>286</v>
       </c>
-      <c r="D59" s="22" t="s">
+      <c r="D59" s="16" t="s">
         <v>373</v>
       </c>
       <c r="E59" t="s">
@@ -5316,7 +5344,7 @@
       <c r="C60" t="s">
         <v>355</v>
       </c>
-      <c r="D60" s="22" t="s">
+      <c r="D60" s="16" t="s">
         <v>376</v>
       </c>
       <c r="E60" t="s">
@@ -5327,7 +5355,7 @@
       <c r="C61" t="s">
         <v>355</v>
       </c>
-      <c r="D61" s="22" t="s">
+      <c r="D61" s="16" t="s">
         <v>377</v>
       </c>
       <c r="E61" t="s">
@@ -5338,7 +5366,7 @@
       <c r="C62" t="s">
         <v>332</v>
       </c>
-      <c r="D62" s="22" t="s">
+      <c r="D62" s="16" t="s">
         <v>379</v>
       </c>
       <c r="E62" t="s">
@@ -5349,7 +5377,7 @@
       <c r="C63" t="s">
         <v>332</v>
       </c>
-      <c r="D63" s="22" t="s">
+      <c r="D63" s="16" t="s">
         <v>381</v>
       </c>
       <c r="E63" t="s">
@@ -5360,7 +5388,7 @@
       <c r="C64" t="s">
         <v>296</v>
       </c>
-      <c r="D64" s="22" t="s">
+      <c r="D64" s="16" t="s">
         <v>383</v>
       </c>
       <c r="E64" t="s">
@@ -5371,7 +5399,7 @@
       <c r="C65" t="s">
         <v>296</v>
       </c>
-      <c r="D65" s="22" t="s">
+      <c r="D65" s="16" t="s">
         <v>385</v>
       </c>
       <c r="E65" t="s">
@@ -5382,7 +5410,7 @@
       <c r="C66" t="s">
         <v>332</v>
       </c>
-      <c r="D66" s="22" t="s">
+      <c r="D66" s="16" t="s">
         <v>388</v>
       </c>
       <c r="E66" t="s">
@@ -5393,7 +5421,7 @@
       <c r="C67" t="s">
         <v>332</v>
       </c>
-      <c r="D67" s="22" t="s">
+      <c r="D67" s="16" t="s">
         <v>389</v>
       </c>
       <c r="E67" t="s">
@@ -5404,7 +5432,7 @@
       <c r="C68" t="s">
         <v>287</v>
       </c>
-      <c r="D68" s="22" t="s">
+      <c r="D68" s="16" t="s">
         <v>391</v>
       </c>
       <c r="E68" t="s">
@@ -5415,7 +5443,7 @@
       <c r="C69" t="s">
         <v>287</v>
       </c>
-      <c r="D69" s="22" t="s">
+      <c r="D69" s="16" t="s">
         <v>393</v>
       </c>
       <c r="E69" t="s">
@@ -5426,7 +5454,7 @@
       <c r="C70" t="s">
         <v>286</v>
       </c>
-      <c r="D70" s="22" t="s">
+      <c r="D70" s="16" t="s">
         <v>396</v>
       </c>
       <c r="E70" t="s">
@@ -5437,7 +5465,7 @@
       <c r="C71" t="s">
         <v>287</v>
       </c>
-      <c r="D71" s="22" t="s">
+      <c r="D71" s="16" t="s">
         <v>397</v>
       </c>
       <c r="E71" t="s">
@@ -5448,7 +5476,7 @@
       <c r="C72" t="s">
         <v>286</v>
       </c>
-      <c r="D72" s="22" t="s">
+      <c r="D72" s="16" t="s">
         <v>399</v>
       </c>
       <c r="E72" t="s">
@@ -5459,7 +5487,7 @@
       <c r="C73" t="s">
         <v>287</v>
       </c>
-      <c r="D73" s="22" t="s">
+      <c r="D73" s="16" t="s">
         <v>401</v>
       </c>
       <c r="E73" t="s">
@@ -5470,7 +5498,7 @@
       <c r="C74" t="s">
         <v>286</v>
       </c>
-      <c r="D74" s="22" t="s">
+      <c r="D74" s="16" t="s">
         <v>403</v>
       </c>
       <c r="E74" t="s">
@@ -5481,7 +5509,7 @@
       <c r="C75" t="s">
         <v>332</v>
       </c>
-      <c r="D75" s="22" t="s">
+      <c r="D75" s="16" t="s">
         <v>405</v>
       </c>
       <c r="E75" t="s">
@@ -5492,7 +5520,7 @@
       <c r="C76" t="s">
         <v>332</v>
       </c>
-      <c r="D76" s="22" t="s">
+      <c r="D76" s="16" t="s">
         <v>407</v>
       </c>
       <c r="E76" t="s">
@@ -5503,7 +5531,7 @@
       <c r="C77" t="s">
         <v>297</v>
       </c>
-      <c r="D77" s="22" t="s">
+      <c r="D77" s="16" t="s">
         <v>409</v>
       </c>
       <c r="E77" t="s">
@@ -5514,7 +5542,7 @@
       <c r="C78" t="s">
         <v>286</v>
       </c>
-      <c r="D78" s="22" t="s">
+      <c r="D78" s="16" t="s">
         <v>412</v>
       </c>
       <c r="E78" t="s">
@@ -5525,7 +5553,7 @@
       <c r="C79" t="s">
         <v>287</v>
       </c>
-      <c r="D79" s="22" t="s">
+      <c r="D79" s="16" t="s">
         <v>413</v>
       </c>
       <c r="E79" t="s">

--- a/dev_stuffs/palmon.xlsx
+++ b/dev_stuffs/palmon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\Palmon\dev_stuffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5991219-BD7F-4ABB-9E9C-7C0964B894D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60CE7E5A-BB22-4DD2-BF61-82EB482AC434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{41DCFB66-B5C9-4783-B084-0F93150E63F9}"/>
+    <workbookView xWindow="30612" yWindow="-6720" windowWidth="30936" windowHeight="18816" activeTab="2" xr2:uid="{41DCFB66-B5C9-4783-B084-0F93150E63F9}"/>
   </bookViews>
   <sheets>
     <sheet name="材料" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="495">
   <si>
     <t>阶段1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1792,6 +1792,13 @@
   </si>
   <si>
     <t>聚合物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tinkers_advanced:proto_refining</t>
+  </si>
+  <si>
+    <t>持续挖掘获得时运和抢夺</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2037,6 +2044,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2045,9 +2055,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2699,13 +2706,13 @@
         <v>16</v>
       </c>
       <c r="R22" s="13"/>
-      <c r="S22" s="23" t="s">
+      <c r="S22" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="T22" s="23"/>
-      <c r="U22" s="23"/>
-      <c r="V22" s="23"/>
-      <c r="W22" s="23"/>
+      <c r="T22" s="20"/>
+      <c r="U22" s="20"/>
+      <c r="V22" s="20"/>
+      <c r="W22" s="20"/>
     </row>
     <row r="23" spans="2:23" x14ac:dyDescent="0.2">
       <c r="E23" s="2"/>
@@ -3372,65 +3379,65 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="G2" s="21" t="s">
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="G2" s="22" t="s">
         <v>209</v>
       </c>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20" t="s">
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="20"/>
-      <c r="T5" s="20"/>
-      <c r="U5" s="20"/>
-      <c r="V5" s="20" t="s">
+      <c r="N5" s="21"/>
+      <c r="O5" s="21"/>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="21"/>
+      <c r="R5" s="21"/>
+      <c r="S5" s="21"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="21"/>
+      <c r="V5" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="W5" s="20"/>
-      <c r="X5" s="20" t="s">
+      <c r="W5" s="21"/>
+      <c r="X5" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="Y5" s="20"/>
-      <c r="Z5" s="20"/>
-      <c r="AA5" s="20"/>
-      <c r="AB5" s="20"/>
-      <c r="AC5" s="20"/>
-      <c r="AD5" s="20"/>
-      <c r="AE5" s="20"/>
-      <c r="AF5" s="20"/>
-      <c r="AG5" s="20"/>
+      <c r="Y5" s="21"/>
+      <c r="Z5" s="21"/>
+      <c r="AA5" s="21"/>
+      <c r="AB5" s="21"/>
+      <c r="AC5" s="21"/>
+      <c r="AD5" s="21"/>
+      <c r="AE5" s="21"/>
+      <c r="AF5" s="21"/>
+      <c r="AG5" s="21"/>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C6" s="4" t="s">
@@ -3528,7 +3535,7 @@
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="22" t="s">
         <v>78</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -3626,7 +3633,7 @@
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B8" s="21"/>
+      <c r="B8" s="22"/>
       <c r="C8" s="4" t="s">
         <v>84</v>
       </c>
@@ -3692,7 +3699,7 @@
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B9" s="21"/>
+      <c r="B9" s="22"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -3728,7 +3735,7 @@
       <c r="AG9" s="4"/>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="22" t="s">
         <v>79</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -3824,7 +3831,7 @@
       <c r="AG10" s="4"/>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B11" s="21"/>
+      <c r="B11" s="22"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4" t="s">
         <v>91</v>
@@ -3888,7 +3895,7 @@
       <c r="AG11" s="4"/>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B12" s="21"/>
+      <c r="B12" s="22"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -3928,7 +3935,7 @@
       <c r="AG12" s="4"/>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B13" s="21"/>
+      <c r="B13" s="22"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -4756,7 +4763,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A68B449-6496-4C27-B0D0-42A49C13CB56}">
-  <dimension ref="C2:E116"/>
+  <dimension ref="C2:E117"/>
   <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="41.375" customWidth="1"/>
@@ -5965,6 +5972,17 @@
       </c>
       <c r="E116" t="s">
         <v>487</v>
+      </c>
+    </row>
+    <row r="117" spans="3:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C117" t="s">
+        <v>286</v>
+      </c>
+      <c r="D117" t="s">
+        <v>493</v>
+      </c>
+      <c r="E117" t="s">
+        <v>494</v>
       </c>
     </row>
   </sheetData>
